--- a/smart_traffic_v1/智能交通设备统计_2026-05-26.xlsx
+++ b/smart_traffic_v1/智能交通设备统计_2026-05-26.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12495" activeTab="4"/>
+    <workbookView windowWidth="28800" windowHeight="12495" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="信号灯" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="42">
   <si>
     <t>路口名称</t>
   </si>
@@ -93,21 +93,12 @@
     <t>取电说明</t>
   </si>
   <si>
+    <t>设备服役时长（年）</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>十字路口</t>
-  </si>
-  <si>
-    <t>丁字路口</t>
-  </si>
-  <si>
-    <t>行人过街</t>
-  </si>
-  <si>
-    <t>其他</t>
-  </si>
-  <si>
     <t>抓拍类型</t>
   </si>
   <si>
@@ -129,7 +120,7 @@
     <t>监控球机数量</t>
   </si>
   <si>
-    <t>信号灯检测器数量</t>
+    <t>信号检测器数量</t>
   </si>
   <si>
     <t>取网说明</t>
@@ -150,36 +141,6 @@
     <t>监控标牌数量</t>
   </si>
   <si>
-    <t>sdsadsa</t>
-  </si>
-  <si>
-    <t>ss</t>
-  </si>
-  <si>
-    <t>ssss</t>
-  </si>
-  <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>2033-06-29</t>
-  </si>
-  <si>
-    <t>在保</t>
-  </si>
-  <si>
-    <t>市电</t>
-  </si>
-  <si>
-    <t>光纤</t>
-  </si>
-  <si>
-    <t>过保</t>
-  </si>
-  <si>
     <t>卡口类型</t>
   </si>
   <si>
@@ -192,49 +153,10 @@
     <t>标牌数量</t>
   </si>
   <si>
-    <t>雷达测速卡口</t>
-  </si>
-  <si>
-    <t>闯禁区卡口</t>
-  </si>
-  <si>
-    <t>大货车不靠右行驶卡口</t>
-  </si>
-  <si>
-    <t>单行道卡口</t>
-  </si>
-  <si>
     <t>设备名称</t>
   </si>
   <si>
     <t>设备类型</t>
-  </si>
-  <si>
-    <t>网络交换设备</t>
-  </si>
-  <si>
-    <t>网络安全设备</t>
-  </si>
-  <si>
-    <t>服务器</t>
-  </si>
-  <si>
-    <t>存储设备</t>
-  </si>
-  <si>
-    <t>显示设备</t>
-  </si>
-  <si>
-    <t>操作设备</t>
-  </si>
-  <si>
-    <t>消防设备</t>
-  </si>
-  <si>
-    <t>用电设备</t>
-  </si>
-  <si>
-    <t>空调设备</t>
   </si>
 </sst>
 </file>
@@ -247,14 +169,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -710,148 +625,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1203,10 +1118,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="3" width="6" customWidth="1"/>
+    <col min="1" max="1" width="9.9" customWidth="1"/>
+    <col min="2" max="2" width="10.0916666666667" customWidth="1"/>
+    <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
     <col min="6" max="6" width="15.275" customWidth="1"/>
@@ -1221,9 +1138,10 @@
     <col min="18" max="18" width="9" customWidth="1"/>
     <col min="19" max="19" width="7" customWidth="1"/>
     <col min="20" max="20" width="6" customWidth="1"/>
+    <col min="21" max="21" width="17.3083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:21">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1284,245 +1202,196 @@
       <c r="T1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:20">
-      <c r="A2" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="E2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2"/>
+        <v>21</v>
+      </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="E3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3"/>
+        <v>21</v>
+      </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
       <c r="E4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4"/>
+        <v>21</v>
+      </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
       <c r="E5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5"/>
+        <v>21</v>
+      </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1534,7 +1403,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="3" width="6" customWidth="1"/>
@@ -1551,7 +1420,7 @@
     <col min="18" max="18" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1580,247 +1449,210 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" t="s">
         <v>25</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>26</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>27</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>28</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>29</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>30</v>
       </c>
-      <c r="P1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>32</v>
-      </c>
-      <c r="R1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" t="s">
+      <c r="S1" t="s">
         <v>20</v>
       </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
+    </row>
+    <row r="2" spans="1:19">
       <c r="D2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2"/>
+        <v>21</v>
+      </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="D3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3"/>
+        <v>21</v>
+      </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
       <c r="D4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4"/>
+        <v>21</v>
+      </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="D5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5"/>
+        <v>21</v>
+      </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1832,11 +1664,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="3" width="6" customWidth="1"/>
+    <col min="2" max="2" width="9.125" customWidth="1"/>
+    <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -1846,12 +1679,12 @@
     <col min="13" max="14" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -1875,106 +1708,21 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="M1" t="s">
         <v>19</v>
       </c>
       <c r="N1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1987,7 +1735,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2002,12 +1750,12 @@
     <col min="13" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2031,202 +1779,189 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K1" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="L1" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="M1" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="N1" t="s">
         <v>19</v>
       </c>
       <c r="O1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+        <v>30</v>
+      </c>
+      <c r="P1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2"/>
+        <v>21</v>
+      </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3"/>
+        <v>21</v>
+      </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4"/>
+        <v>21</v>
+      </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5"/>
+        <v>21</v>
+      </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -2238,24 +1973,26 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.125" customWidth="1"/>
-    <col min="2" max="2" width="16.375" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="9" width="6" customWidth="1"/>
+    <col min="2" max="2" width="13.0416666666667" customWidth="1"/>
+    <col min="3" max="3" width="13.975" customWidth="1"/>
+    <col min="4" max="4" width="10.2333333333333" customWidth="1"/>
+    <col min="5" max="5" width="11.0166666666667" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
+    <col min="7" max="7" width="9.29166666666667" customWidth="1"/>
+    <col min="8" max="8" width="10.3083333333333" customWidth="1"/>
+    <col min="9" max="9" width="11.55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -2278,248 +2015,53 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
+      <c r="J1" t="s">
         <v>20</v>
       </c>
-      <c r="B2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2"/>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="I2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3"/>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="I3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4"/>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="I4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5"/>
-      <c r="H5" t="s">
-        <v>20</v>
-      </c>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="I5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6"/>
-      <c r="H6" t="s">
-        <v>20</v>
-      </c>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="I6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7"/>
-      <c r="H7" t="s">
-        <v>20</v>
-      </c>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="I7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8"/>
-      <c r="H8" t="s">
-        <v>20</v>
-      </c>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="I8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9"/>
-      <c r="H9" t="s">
-        <v>20</v>
-      </c>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="I9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10"/>
-      <c r="H10" t="s">
-        <v>20</v>
-      </c>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="I10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
